--- a/Data/Export/Common/TerrainType_地形类型.xlsx
+++ b/Data/Export/Common/TerrainType_地形类型.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\sango_infinity\Data\Export\Common\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D2D2D9-D29F-414B-B8BC-8C880E0CAF15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4E8BC-B140-48DC-8012-A2A20488C955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4350" yWindow="1170" windowWidth="21600" windowHeight="14010" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TerrainTypes" sheetId="36" r:id="rId1"/>
@@ -1054,29 +1054,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B0F1D98-4B0B-4096-90A4-E28636B1D41A}">
   <dimension ref="A1:AA46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="19.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.77734375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.625" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.21875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.25" style="2" customWidth="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="10" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12"/>
       <c r="B1" s="9" t="s">
         <v>4</v>
@@ -1139,7 +1139,7 @@
       <c r="Z1" s="9"/>
       <c r="AA1" s="7"/>
     </row>
-    <row r="2" spans="1:27" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,7 +1168,7 @@
       <c r="Z2" s="2"/>
       <c r="AA2" s="2"/>
     </row>
-    <row r="3" spans="1:27" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" s="5" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1233,7 +1233,7 @@
       <c r="Z3" s="8"/>
       <c r="AA3" s="8"/>
     </row>
-    <row r="4" spans="1:27" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1321,7 +1321,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>2</v>
@@ -1347,7 +1347,7 @@
       <c r="X5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A6" s="3"/>
       <c r="B6" s="2">
         <v>1</v>
@@ -1406,7 +1406,7 @@
       <c r="X6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B7" s="2">
         <v>2</v>
       </c>
@@ -1464,7 +1464,7 @@
       <c r="X7" s="4"/>
       <c r="Z7" s="4"/>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B8" s="2">
         <v>3</v>
       </c>
@@ -1522,7 +1522,7 @@
       <c r="X8" s="4"/>
       <c r="Z8" s="4"/>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B9" s="2">
         <v>4</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>2</v>
@@ -1580,7 +1580,7 @@
       <c r="X9" s="4"/>
       <c r="Z9" s="4"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B10" s="2">
         <v>5</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>98</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>2</v>
@@ -1638,7 +1638,7 @@
       <c r="X10" s="4"/>
       <c r="Z10" s="4"/>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B11" s="2">
         <v>6</v>
       </c>
@@ -1670,7 +1670,7 @@
         <v>140</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>2</v>
@@ -1696,7 +1696,7 @@
       <c r="X11" s="4"/>
       <c r="Z11" s="4"/>
     </row>
-    <row r="12" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B12" s="16">
         <v>7</v>
       </c>
@@ -1727,8 +1727,8 @@
       <c r="K12" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>2</v>
+      <c r="L12" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>2</v>
@@ -1754,7 +1754,7 @@
       <c r="X12" s="18"/>
       <c r="Z12" s="18"/>
     </row>
-    <row r="13" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B13" s="16">
         <v>8</v>
       </c>
@@ -1785,8 +1785,8 @@
       <c r="K13" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="L13" s="16" t="s">
-        <v>2</v>
+      <c r="L13" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="M13" s="16" t="s">
         <v>2</v>
@@ -1812,7 +1812,7 @@
       <c r="X13" s="18"/>
       <c r="Z13" s="18"/>
     </row>
-    <row r="14" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" s="16" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16">
         <v>9</v>
       </c>
@@ -1843,8 +1843,8 @@
       <c r="K14" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>2</v>
+      <c r="L14" s="2" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>2</v>
@@ -1870,7 +1870,7 @@
       <c r="X14" s="18"/>
       <c r="Z14" s="18"/>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B15" s="2">
         <v>10</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>141</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>2</v>
@@ -1928,7 +1928,7 @@
       <c r="X15" s="4"/>
       <c r="Z15" s="4"/>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
       <c r="B16" s="2">
         <v>11</v>
       </c>
@@ -1986,7 +1986,7 @@
       <c r="X16" s="4"/>
       <c r="Z16" s="4"/>
     </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B17" s="2">
         <v>12</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>136</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>2</v>
@@ -2044,7 +2044,7 @@
       <c r="X17" s="4"/>
       <c r="Z17" s="4"/>
     </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B18" s="2">
         <v>13</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>117</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>2</v>
@@ -2102,7 +2102,7 @@
       <c r="X18" s="4"/>
       <c r="Z18" s="4"/>
     </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B19" s="2">
         <v>14</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>98</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>2</v>
@@ -2160,7 +2160,7 @@
       <c r="X19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B20" s="2">
         <v>15</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>2</v>
@@ -2218,7 +2218,7 @@
       <c r="X20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B21" s="2">
         <v>16</v>
       </c>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>2</v>
@@ -2276,7 +2276,7 @@
       <c r="X21" s="4"/>
       <c r="Z21" s="4"/>
     </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B22" s="2">
         <v>17</v>
       </c>
@@ -2334,7 +2334,7 @@
       <c r="X22" s="4"/>
       <c r="Z22" s="4"/>
     </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B23" s="2" t="s">
         <v>130</v>
       </c>
@@ -2392,7 +2392,7 @@
       <c r="X23" s="4"/>
       <c r="Z23" s="4"/>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B24" s="2" t="s">
         <v>131</v>
       </c>
@@ -2450,7 +2450,7 @@
       <c r="X24" s="4"/>
       <c r="Z24" s="4"/>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B25" s="2">
         <v>20</v>
       </c>
@@ -2508,7 +2508,7 @@
       <c r="X25" s="4"/>
       <c r="Z25" s="4"/>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B26" s="2">
         <v>21</v>
       </c>
@@ -2566,7 +2566,7 @@
       <c r="X26" s="4"/>
       <c r="Z26" s="4"/>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B27" s="2">
         <v>22</v>
       </c>
@@ -2624,7 +2624,7 @@
       <c r="X27" s="4"/>
       <c r="Z27" s="4"/>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B28" s="2">
         <v>23</v>
       </c>
@@ -2682,7 +2682,7 @@
       <c r="X28" s="4"/>
       <c r="Z28" s="4"/>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B29" s="2">
         <v>24</v>
       </c>
@@ -2740,7 +2740,7 @@
       <c r="X29" s="4"/>
       <c r="Z29" s="4"/>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B30" s="2">
         <v>25</v>
       </c>
@@ -2798,7 +2798,7 @@
       <c r="X30" s="4"/>
       <c r="Z30" s="4"/>
     </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B31" s="2">
         <v>26</v>
       </c>
@@ -2856,7 +2856,7 @@
       <c r="X31" s="4"/>
       <c r="Z31" s="4"/>
     </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B32" s="2">
         <v>27</v>
       </c>
@@ -2914,7 +2914,7 @@
       <c r="X32" s="4"/>
       <c r="Z32" s="4"/>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B33" s="2">
         <v>28</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="X33" s="4"/>
       <c r="Z33" s="4"/>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B34" s="2">
         <v>29</v>
       </c>
@@ -3030,7 +3030,7 @@
       <c r="X34" s="4"/>
       <c r="Z34" s="4"/>
     </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B35" s="2">
         <v>30</v>
       </c>
@@ -3088,7 +3088,7 @@
       <c r="X35" s="4"/>
       <c r="Z35" s="4"/>
     </row>
-    <row r="36" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B36" s="2">
         <v>31</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="X36" s="4"/>
       <c r="Z36" s="4"/>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.15">
       <c r="B37" s="4"/>
       <c r="R37" s="4"/>
       <c r="T37" s="4"/>
@@ -3155,7 +3155,7 @@
       <c r="X37" s="4"/>
       <c r="Z37" s="4"/>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J38" s="6"/>
       <c r="K38" s="6"/>
       <c r="R38" s="4"/>
@@ -3165,7 +3165,7 @@
       <c r="X38" s="4"/>
       <c r="Z38" s="4"/>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J39" s="6"/>
       <c r="K39" s="6"/>
       <c r="R39" s="4"/>
@@ -3175,7 +3175,7 @@
       <c r="X39" s="4"/>
       <c r="Z39" s="4"/>
     </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="R40" s="4"/>
@@ -3185,7 +3185,7 @@
       <c r="X40" s="4"/>
       <c r="Z40" s="4"/>
     </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
       <c r="R41" s="4"/>
@@ -3195,7 +3195,7 @@
       <c r="X41" s="4"/>
       <c r="Z41" s="4"/>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J42" s="6"/>
       <c r="K42" s="6"/>
       <c r="R42" s="4"/>
@@ -3205,7 +3205,7 @@
       <c r="X42" s="4"/>
       <c r="Z42" s="4"/>
     </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J43" s="6"/>
       <c r="K43" s="6"/>
       <c r="R43" s="4"/>
@@ -3215,7 +3215,7 @@
       <c r="X43" s="4"/>
       <c r="Z43" s="4"/>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J44" s="6"/>
       <c r="K44" s="6"/>
       <c r="R44" s="4"/>
@@ -3225,7 +3225,7 @@
       <c r="X44" s="4"/>
       <c r="Z44" s="4"/>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J45" s="6"/>
       <c r="K45" s="6"/>
       <c r="R45" s="4"/>
@@ -3235,7 +3235,7 @@
       <c r="X45" s="4"/>
       <c r="Z45" s="4"/>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.15">
       <c r="J46" s="6"/>
       <c r="K46" s="6"/>
       <c r="R46" s="4"/>
